--- a/Team-Data/2008-09/1-18-2008-09.xlsx
+++ b/Team-Data/2008-09/1-18-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -745,7 +812,7 @@
         <v>11</v>
       </c>
       <c r="AF2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG2" t="n">
         <v>11</v>
@@ -754,13 +821,13 @@
         <v>24</v>
       </c>
       <c r="AI2" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AJ2" t="n">
         <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -769,19 +836,19 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AO2" t="n">
         <v>23</v>
       </c>
       <c r="AP2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AQ2" t="n">
         <v>28</v>
       </c>
       <c r="AR2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS2" t="n">
         <v>21</v>
@@ -790,7 +857,7 @@
         <v>22</v>
       </c>
       <c r="AU2" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV2" t="n">
         <v>6</v>
@@ -799,7 +866,7 @@
         <v>20</v>
       </c>
       <c r="AX2" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AY2" t="n">
         <v>11</v>
@@ -811,7 +878,7 @@
         <v>21</v>
       </c>
       <c r="BB2" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="BC2" t="n">
         <v>12</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -843,88 +910,88 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E3" t="n">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="F3" t="n">
         <v>9</v>
       </c>
       <c r="G3" t="n">
-        <v>0.78</v>
+        <v>0.786</v>
       </c>
       <c r="H3" t="n">
         <v>48.5</v>
       </c>
       <c r="I3" t="n">
-        <v>36.7</v>
+        <v>36.6</v>
       </c>
       <c r="J3" t="n">
-        <v>76.40000000000001</v>
+        <v>76.3</v>
       </c>
       <c r="K3" t="n">
-        <v>0.481</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6.5</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
         <v>17.2</v>
       </c>
       <c r="N3" t="n">
-        <v>0.378</v>
+        <v>0.374</v>
       </c>
       <c r="O3" t="n">
         <v>21.2</v>
       </c>
       <c r="P3" t="n">
-        <v>27.3</v>
+        <v>27.5</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.776</v>
+        <v>0.771</v>
       </c>
       <c r="R3" t="n">
         <v>10.8</v>
       </c>
       <c r="S3" t="n">
-        <v>32.1</v>
+        <v>32</v>
       </c>
       <c r="T3" t="n">
-        <v>43</v>
+        <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.4</v>
+        <v>22.3</v>
       </c>
       <c r="V3" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
-        <v>23.1</v>
+        <v>23.2</v>
       </c>
       <c r="AA3" t="n">
         <v>23.5</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.1</v>
+        <v>100.9</v>
       </c>
       <c r="AC3" t="n">
-        <v>9.300000000000001</v>
+        <v>9.199999999999999</v>
       </c>
       <c r="AD3" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AF3" t="n">
         <v>4</v>
@@ -933,7 +1000,7 @@
         <v>4</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
         <v>13</v>
@@ -951,7 +1018,7 @@
         <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>9</v>
+        <v>12</v>
       </c>
       <c r="AO3" t="n">
         <v>5</v>
@@ -960,16 +1027,16 @@
         <v>5</v>
       </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AS3" t="n">
         <v>5</v>
       </c>
       <c r="AT3" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AU3" t="n">
         <v>5</v>
@@ -981,10 +1048,10 @@
         <v>4</v>
       </c>
       <c r="AX3" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AY3" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AZ3" t="n">
         <v>26</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -1103,7 +1170,7 @@
         <v>-2.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE4" t="n">
         <v>20</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -1207,61 +1274,61 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
         <v>23</v>
       </c>
       <c r="G5" t="n">
-        <v>0.425</v>
+        <v>0.439</v>
       </c>
       <c r="H5" t="n">
         <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.2</v>
+        <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.2</v>
+        <v>83.8</v>
       </c>
       <c r="K5" t="n">
-        <v>0.441</v>
+        <v>0.443</v>
       </c>
       <c r="L5" t="n">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.379</v>
+        <v>0.38</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.8</v>
+        <v>0.798</v>
       </c>
       <c r="R5" t="n">
-        <v>11.5</v>
+        <v>11.6</v>
       </c>
       <c r="S5" t="n">
-        <v>30.3</v>
+        <v>30.1</v>
       </c>
       <c r="T5" t="n">
-        <v>41.8</v>
+        <v>41.7</v>
       </c>
       <c r="U5" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="V5" t="n">
-        <v>14.8</v>
+        <v>14.9</v>
       </c>
       <c r="W5" t="n">
         <v>7.4</v>
@@ -1270,34 +1337,34 @@
         <v>5.5</v>
       </c>
       <c r="Y5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Z5" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.2</v>
+        <v>20.4</v>
       </c>
       <c r="AB5" t="n">
-        <v>98.90000000000001</v>
+        <v>99.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.5</v>
+        <v>-3.1</v>
       </c>
       <c r="AD5" t="n">
-        <v>12</v>
+        <v>3</v>
       </c>
       <c r="AE5" t="n">
         <v>19</v>
       </c>
       <c r="AF5" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG5" t="n">
         <v>19</v>
       </c>
       <c r="AH5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
@@ -1315,13 +1382,13 @@
         <v>20</v>
       </c>
       <c r="AN5" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AO5" t="n">
+        <v>17</v>
+      </c>
+      <c r="AP5" t="n">
         <v>21</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>24</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
@@ -1330,7 +1397,7 @@
         <v>12</v>
       </c>
       <c r="AS5" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AT5" t="n">
         <v>14</v>
@@ -1342,10 +1409,10 @@
         <v>18</v>
       </c>
       <c r="AW5" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AX5" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
         <v>25</v>
@@ -1354,7 +1421,7 @@
         <v>22</v>
       </c>
       <c r="BA5" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -1389,49 +1456,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="E6" t="n">
         <v>31</v>
       </c>
       <c r="F6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="G6" t="n">
-        <v>0.838</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.09999999999999</v>
+        <v>77.8</v>
       </c>
       <c r="K6" t="n">
-        <v>0.479</v>
+        <v>0.478</v>
       </c>
       <c r="L6" t="n">
-        <v>7.5</v>
+        <v>7.4</v>
       </c>
       <c r="M6" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0.363</v>
+        <v>0.36</v>
       </c>
       <c r="O6" t="n">
-        <v>19.1</v>
+        <v>19.2</v>
       </c>
       <c r="P6" t="n">
-        <v>25.2</v>
+        <v>25.4</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R6" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S6" t="n">
         <v>31.1</v>
@@ -1440,34 +1507,34 @@
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V6" t="n">
-        <v>13.1</v>
+        <v>13.3</v>
       </c>
       <c r="W6" t="n">
         <v>8.1</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>3.7</v>
+        <v>3.6</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.5</v>
+        <v>20.7</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21.1</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.4</v>
+        <v>100.9</v>
       </c>
       <c r="AC6" t="n">
-        <v>12.4</v>
+        <v>11.9</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="AE6" t="n">
         <v>3</v>
@@ -1491,22 +1558,22 @@
         <v>3</v>
       </c>
       <c r="AL6" t="n">
+        <v>8</v>
+      </c>
+      <c r="AM6" t="n">
         <v>7</v>
-      </c>
-      <c r="AM6" t="n">
-        <v>6</v>
       </c>
       <c r="AN6" t="n">
         <v>16</v>
       </c>
       <c r="AO6" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AP6" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AQ6" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AR6" t="n">
         <v>21</v>
@@ -1518,7 +1585,7 @@
         <v>15</v>
       </c>
       <c r="AU6" t="n">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="AV6" t="n">
         <v>7</v>
@@ -1533,10 +1600,10 @@
         <v>2</v>
       </c>
       <c r="AZ6" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="BA6" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BB6" t="n">
         <v>9</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -1649,7 +1716,7 @@
         <v>1.4</v>
       </c>
       <c r="AD7" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
@@ -1661,7 +1728,7 @@
         <v>13</v>
       </c>
       <c r="AH7" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AI7" t="n">
         <v>6</v>
@@ -1682,7 +1749,7 @@
         <v>26</v>
       </c>
       <c r="AO7" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AP7" t="n">
         <v>29</v>
@@ -1700,7 +1767,7 @@
         <v>1</v>
       </c>
       <c r="AU7" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -1831,7 +1898,7 @@
         <v>3.2</v>
       </c>
       <c r="AD8" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE8" t="n">
         <v>5</v>
@@ -1849,7 +1916,7 @@
         <v>12</v>
       </c>
       <c r="AJ8" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1879,7 +1946,7 @@
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
         <v>4</v>
@@ -1900,13 +1967,13 @@
         <v>24</v>
       </c>
       <c r="BA8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BB8" t="n">
         <v>5</v>
       </c>
       <c r="BC8" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="BD8" t="n">
         <v>10</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -2016,7 +2083,7 @@
         <v>18</v>
       </c>
       <c r="AE9" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AF9" t="n">
         <v>12</v>
@@ -2055,7 +2122,7 @@
         <v>27</v>
       </c>
       <c r="AR9" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AS9" t="n">
         <v>14</v>
@@ -2082,13 +2149,13 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BB9" t="n">
         <v>28</v>
       </c>
       <c r="BC9" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BD9" t="n">
         <v>10</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -2195,7 +2262,7 @@
         <v>-5.6</v>
       </c>
       <c r="AD10" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE10" t="n">
         <v>24</v>
@@ -2246,13 +2313,13 @@
         <v>8</v>
       </c>
       <c r="AU10" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
         <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -2377,16 +2444,16 @@
         <v>2.9</v>
       </c>
       <c r="AD11" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
       </c>
       <c r="AF11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
@@ -2410,7 +2477,7 @@
         <v>13</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2446,13 +2513,13 @@
         <v>3</v>
       </c>
       <c r="BA11" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB11" t="n">
         <v>21</v>
       </c>
       <c r="BC11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BD11" t="n">
         <v>10</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -2559,7 +2626,7 @@
         <v>-2.1</v>
       </c>
       <c r="AD12" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE12" t="n">
         <v>22</v>
@@ -2583,7 +2650,7 @@
         <v>14</v>
       </c>
       <c r="AL12" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
@@ -2592,10 +2659,10 @@
         <v>15</v>
       </c>
       <c r="AO12" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AP12" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ12" t="n">
         <v>5</v>
@@ -2610,13 +2677,13 @@
         <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AV12" t="n">
         <v>23</v>
       </c>
       <c r="AW12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AX12" t="n">
         <v>10</v>
@@ -2625,10 +2692,10 @@
         <v>24</v>
       </c>
       <c r="AZ12" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="BA12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BB12" t="n">
         <v>3</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -2777,7 +2844,7 @@
         <v>25</v>
       </c>
       <c r="AP13" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AQ13" t="n">
         <v>25</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -2845,16 +2912,16 @@
         </is>
       </c>
       <c r="D14" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="E14" t="n">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="F14" t="n">
         <v>8</v>
       </c>
       <c r="G14" t="n">
-        <v>0.789</v>
+        <v>0.795</v>
       </c>
       <c r="H14" t="n">
         <v>48</v>
@@ -2863,7 +2930,7 @@
         <v>39.7</v>
       </c>
       <c r="J14" t="n">
-        <v>83.8</v>
+        <v>83.7</v>
       </c>
       <c r="K14" t="n">
         <v>0.474</v>
@@ -2872,31 +2939,31 @@
         <v>7</v>
       </c>
       <c r="M14" t="n">
-        <v>18.6</v>
+        <v>18.4</v>
       </c>
       <c r="N14" t="n">
-        <v>0.378</v>
+        <v>0.383</v>
       </c>
       <c r="O14" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="P14" t="n">
-        <v>27.9</v>
+        <v>27.6</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.77</v>
+        <v>0.771</v>
       </c>
       <c r="R14" t="n">
-        <v>12.2</v>
+        <v>12.1</v>
       </c>
       <c r="S14" t="n">
-        <v>31.7</v>
+        <v>31.9</v>
       </c>
       <c r="T14" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
-        <v>23.2</v>
+        <v>23.1</v>
       </c>
       <c r="V14" t="n">
         <v>13.7</v>
@@ -2905,28 +2972,28 @@
         <v>8.699999999999999</v>
       </c>
       <c r="X14" t="n">
-        <v>5</v>
+        <v>5.1</v>
       </c>
       <c r="Y14" t="n">
         <v>4.3</v>
       </c>
       <c r="Z14" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="AA14" t="n">
-        <v>23.3</v>
+        <v>23.1</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.6</v>
       </c>
       <c r="AC14" t="n">
-        <v>7.8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="AE14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AF14" t="n">
         <v>2</v>
@@ -2953,16 +3020,16 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AO14" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AP14" t="n">
         <v>3</v>
       </c>
       <c r="AQ14" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AR14" t="n">
         <v>7</v>
@@ -2974,7 +3041,7 @@
         <v>3</v>
       </c>
       <c r="AU14" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AV14" t="n">
         <v>11</v>
@@ -2983,7 +3050,7 @@
         <v>3</v>
       </c>
       <c r="AX14" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AY14" t="n">
         <v>8</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -3209,58 +3276,58 @@
         </is>
       </c>
       <c r="D16" t="n">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="F16" t="n">
         <v>18</v>
       </c>
       <c r="G16" t="n">
-        <v>0.55</v>
+        <v>0.538</v>
       </c>
       <c r="H16" t="n">
         <v>48.4</v>
       </c>
       <c r="I16" t="n">
-        <v>36.4</v>
+        <v>36.2</v>
       </c>
       <c r="J16" t="n">
-        <v>81.2</v>
+        <v>81.09999999999999</v>
       </c>
       <c r="K16" t="n">
-        <v>0.448</v>
+        <v>0.447</v>
       </c>
       <c r="L16" t="n">
-        <v>6.9</v>
+        <v>6.8</v>
       </c>
       <c r="M16" t="n">
-        <v>19.3</v>
+        <v>19.2</v>
       </c>
       <c r="N16" t="n">
-        <v>0.36</v>
+        <v>0.355</v>
       </c>
       <c r="O16" t="n">
-        <v>17.1</v>
+        <v>17.2</v>
       </c>
       <c r="P16" t="n">
-        <v>23.1</v>
+        <v>23.3</v>
       </c>
       <c r="Q16" t="n">
-        <v>0.739</v>
+        <v>0.738</v>
       </c>
       <c r="R16" t="n">
-        <v>10.7</v>
+        <v>10.8</v>
       </c>
       <c r="S16" t="n">
-        <v>29.4</v>
+        <v>29.5</v>
       </c>
       <c r="T16" t="n">
-        <v>40.1</v>
+        <v>40.3</v>
       </c>
       <c r="U16" t="n">
-        <v>20</v>
+        <v>19.9</v>
       </c>
       <c r="V16" t="n">
         <v>12.8</v>
@@ -3269,28 +3336,28 @@
         <v>8.199999999999999</v>
       </c>
       <c r="X16" t="n">
-        <v>5.6</v>
+        <v>5.5</v>
       </c>
       <c r="Y16" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="Z16" t="n">
         <v>21</v>
       </c>
       <c r="AA16" t="n">
-        <v>19.7</v>
+        <v>19.8</v>
       </c>
       <c r="AB16" t="n">
-        <v>96.7</v>
+        <v>96.5</v>
       </c>
       <c r="AC16" t="n">
-        <v>0.1</v>
+        <v>-0.2</v>
       </c>
       <c r="AD16" t="n">
-        <v>12</v>
+        <v>18</v>
       </c>
       <c r="AE16" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AF16" t="n">
         <v>15</v>
@@ -3299,28 +3366,28 @@
         <v>15</v>
       </c>
       <c r="AH16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI16" t="n">
-        <v>16</v>
+        <v>19</v>
       </c>
       <c r="AJ16" t="n">
         <v>13</v>
       </c>
       <c r="AK16" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AL16" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AM16" t="n">
         <v>11</v>
       </c>
       <c r="AN16" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AO16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AP16" t="n">
         <v>23</v>
@@ -3329,25 +3396,25 @@
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AS16" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AT16" t="n">
         <v>23</v>
       </c>
       <c r="AU16" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AV16" t="n">
         <v>4</v>
       </c>
       <c r="AW16" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>10</v>
@@ -3362,7 +3429,7 @@
         <v>22</v>
       </c>
       <c r="BC16" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BD16" t="n">
         <v>10</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -3391,28 +3458,28 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E17" t="n">
         <v>20</v>
       </c>
       <c r="F17" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="G17" t="n">
-        <v>0.476</v>
+        <v>0.465</v>
       </c>
       <c r="H17" t="n">
-        <v>48.4</v>
+        <v>48.3</v>
       </c>
       <c r="I17" t="n">
         <v>36.5</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L17" t="n">
         <v>5.5</v>
@@ -3421,31 +3488,31 @@
         <v>15.7</v>
       </c>
       <c r="N17" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O17" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q17" t="n">
-        <v>0.783</v>
+        <v>0.782</v>
       </c>
       <c r="R17" t="n">
         <v>12.5</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>42.1</v>
+        <v>41.8</v>
       </c>
       <c r="U17" t="n">
         <v>21.2</v>
       </c>
       <c r="V17" t="n">
-        <v>14.5</v>
+        <v>14.6</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,16 +3524,16 @@
         <v>5</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.7</v>
+        <v>22.6</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.09999999999999</v>
+        <v>98</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.8</v>
+        <v>0.5</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,22 +3542,22 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
       </c>
       <c r="AJ17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AK17" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AL17" t="n">
         <v>22</v>
@@ -3502,7 +3569,7 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
         <v>13</v>
@@ -3514,7 +3581,7 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>22</v>
+        <v>26</v>
       </c>
       <c r="AT17" t="n">
         <v>13</v>
@@ -3526,7 +3593,7 @@
         <v>17</v>
       </c>
       <c r="AW17" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3535,16 +3602,16 @@
         <v>15</v>
       </c>
       <c r="AZ17" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="BA17" t="n">
         <v>6</v>
       </c>
       <c r="BB17" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -3651,13 +3718,13 @@
         <v>-3.9</v>
       </c>
       <c r="AD18" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AG18" t="n">
         <v>24</v>
@@ -3687,10 +3754,10 @@
         <v>15</v>
       </c>
       <c r="AP18" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ18" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AR18" t="n">
         <v>5</v>
@@ -3702,7 +3769,7 @@
         <v>12</v>
       </c>
       <c r="AU18" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AV18" t="n">
         <v>15</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-3</v>
       </c>
       <c r="AD19" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3860,10 +3927,10 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AN19" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>7</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -4036,7 +4103,7 @@
         <v>28</v>
       </c>
       <c r="AK20" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL20" t="n">
         <v>9</v>
@@ -4048,7 +4115,7 @@
         <v>4</v>
       </c>
       <c r="AO20" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AP20" t="n">
         <v>26</v>
@@ -4060,7 +4127,7 @@
         <v>28</v>
       </c>
       <c r="AS20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AT20" t="n">
         <v>29</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -4206,7 +4273,7 @@
         <v>20</v>
       </c>
       <c r="AG21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH21" t="n">
         <v>24</v>
@@ -4227,7 +4294,7 @@
         <v>1</v>
       </c>
       <c r="AN21" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AO21" t="n">
         <v>24</v>
@@ -4248,7 +4315,7 @@
         <v>10</v>
       </c>
       <c r="AU21" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AV21" t="n">
         <v>21</v>
@@ -4260,7 +4327,7 @@
         <v>30</v>
       </c>
       <c r="AY21" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AZ21" t="n">
         <v>5</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -4301,28 +4368,28 @@
         </is>
       </c>
       <c r="D22" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E22" t="n">
         <v>8</v>
       </c>
       <c r="F22" t="n">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G22" t="n">
-        <v>0.19</v>
+        <v>0.195</v>
       </c>
       <c r="H22" t="n">
         <v>48.2</v>
       </c>
       <c r="I22" t="n">
-        <v>36.3</v>
+        <v>36.4</v>
       </c>
       <c r="J22" t="n">
-        <v>81.5</v>
+        <v>81.7</v>
       </c>
       <c r="K22" t="n">
-        <v>0.446</v>
+        <v>0.445</v>
       </c>
       <c r="L22" t="n">
         <v>3.9</v>
@@ -4331,28 +4398,28 @@
         <v>10.5</v>
       </c>
       <c r="N22" t="n">
-        <v>0.367</v>
+        <v>0.368</v>
       </c>
       <c r="O22" t="n">
-        <v>18.8</v>
+        <v>18.7</v>
       </c>
       <c r="P22" t="n">
-        <v>24.7</v>
+        <v>24.6</v>
       </c>
       <c r="Q22" t="n">
-        <v>0.762</v>
+        <v>0.763</v>
       </c>
       <c r="R22" t="n">
-        <v>11.5</v>
+        <v>11.7</v>
       </c>
       <c r="S22" t="n">
         <v>31</v>
       </c>
       <c r="T22" t="n">
-        <v>42.6</v>
+        <v>42.7</v>
       </c>
       <c r="U22" t="n">
-        <v>20</v>
+        <v>20.1</v>
       </c>
       <c r="V22" t="n">
         <v>16.5</v>
@@ -4361,25 +4428,25 @@
         <v>7</v>
       </c>
       <c r="X22" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Y22" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="Z22" t="n">
-        <v>20.8</v>
+        <v>20.9</v>
       </c>
       <c r="AA22" t="n">
         <v>20.3</v>
       </c>
       <c r="AB22" t="n">
-        <v>95.3</v>
+        <v>95.40000000000001</v>
       </c>
       <c r="AC22" t="n">
-        <v>-7</v>
+        <v>-6.9</v>
       </c>
       <c r="AD22" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE22" t="n">
         <v>29</v>
@@ -4391,16 +4458,16 @@
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AI22" t="n">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="AJ22" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AK22" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AL22" t="n">
         <v>30</v>
@@ -4415,10 +4482,10 @@
         <v>17</v>
       </c>
       <c r="AP22" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AQ22" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AR22" t="n">
         <v>11</v>
@@ -4430,7 +4497,7 @@
         <v>9</v>
       </c>
       <c r="AU22" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AV22" t="n">
         <v>30</v>
@@ -4442,13 +4509,13 @@
         <v>20</v>
       </c>
       <c r="AY22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AZ22" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BA22" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB22" t="n">
         <v>25</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>8.6</v>
       </c>
       <c r="AD23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE23" t="n">
         <v>1</v>
@@ -4579,7 +4646,7 @@
         <v>17</v>
       </c>
       <c r="AJ23" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AK23" t="n">
         <v>8</v>
@@ -4594,7 +4661,7 @@
         <v>1</v>
       </c>
       <c r="AO23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AP23" t="n">
         <v>7</v>
@@ -4609,7 +4676,7 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
@@ -4624,7 +4691,7 @@
         <v>4</v>
       </c>
       <c r="AY23" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AZ23" t="n">
         <v>7</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AE24" t="n">
         <v>16</v>
@@ -4764,7 +4831,7 @@
         <v>14</v>
       </c>
       <c r="AK24" t="n">
-        <v>11</v>
+        <v>9</v>
       </c>
       <c r="AL24" t="n">
         <v>29</v>
@@ -4776,7 +4843,7 @@
         <v>27</v>
       </c>
       <c r="AO24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AP24" t="n">
         <v>15</v>
@@ -4818,7 +4885,7 @@
         <v>23</v>
       </c>
       <c r="BC24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -4847,88 +4914,88 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E25" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="F25" t="n">
         <v>15</v>
       </c>
       <c r="G25" t="n">
-        <v>0.605</v>
+        <v>0.595</v>
       </c>
       <c r="H25" t="n">
         <v>48.3</v>
       </c>
       <c r="I25" t="n">
-        <v>38.7</v>
+        <v>38.6</v>
       </c>
       <c r="J25" t="n">
         <v>77.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.499</v>
+        <v>0.498</v>
       </c>
       <c r="L25" t="n">
-        <v>6.8</v>
+        <v>6.9</v>
       </c>
       <c r="M25" t="n">
         <v>17.8</v>
       </c>
       <c r="N25" t="n">
-        <v>0.385</v>
+        <v>0.388</v>
       </c>
       <c r="O25" t="n">
-        <v>20.6</v>
+        <v>20.4</v>
       </c>
       <c r="P25" t="n">
-        <v>27</v>
+        <v>26.9</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.763</v>
+        <v>0.76</v>
       </c>
       <c r="R25" t="n">
-        <v>9.699999999999999</v>
+        <v>9.6</v>
       </c>
       <c r="S25" t="n">
-        <v>31.3</v>
+        <v>31.5</v>
       </c>
       <c r="T25" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U25" t="n">
-        <v>21.7</v>
+        <v>21.5</v>
       </c>
       <c r="V25" t="n">
-        <v>16.1</v>
+        <v>16.2</v>
       </c>
       <c r="W25" t="n">
-        <v>6.3</v>
+        <v>6.4</v>
       </c>
       <c r="X25" t="n">
-        <v>4.8</v>
+        <v>4.9</v>
       </c>
       <c r="Y25" t="n">
         <v>4.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.4</v>
+        <v>20.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.2</v>
+        <v>22.1</v>
       </c>
       <c r="AB25" t="n">
-        <v>104.8</v>
+        <v>104.5</v>
       </c>
       <c r="AC25" t="n">
         <v>1.8</v>
       </c>
       <c r="AD25" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="AE25" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AF25" t="n">
         <v>8</v>
@@ -4949,7 +5016,7 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AM25" t="n">
         <v>16</v>
@@ -4964,19 +5031,19 @@
         <v>6</v>
       </c>
       <c r="AQ25" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
       </c>
       <c r="AS25" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="AV25" t="n">
         <v>28</v>
@@ -4985,7 +5052,7 @@
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="AY25" t="n">
         <v>6</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -5029,106 +5096,106 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="E26" t="n">
         <v>24</v>
       </c>
       <c r="F26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="G26" t="n">
-        <v>0.615</v>
+        <v>0.6</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36.1</v>
+        <v>35.9</v>
       </c>
       <c r="J26" t="n">
-        <v>78.59999999999999</v>
+        <v>78.8</v>
       </c>
       <c r="K26" t="n">
-        <v>0.459</v>
+        <v>0.456</v>
       </c>
       <c r="L26" t="n">
-        <v>7.5</v>
+        <v>7.6</v>
       </c>
       <c r="M26" t="n">
-        <v>19.6</v>
+        <v>19.7</v>
       </c>
       <c r="N26" t="n">
-        <v>0.382</v>
+        <v>0.383</v>
       </c>
       <c r="O26" t="n">
-        <v>18.8</v>
+        <v>18.6</v>
       </c>
       <c r="P26" t="n">
-        <v>24.5</v>
+        <v>24.2</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.77</v>
+        <v>0.767</v>
       </c>
       <c r="R26" t="n">
         <v>13</v>
       </c>
       <c r="S26" t="n">
-        <v>27.6</v>
+        <v>27.7</v>
       </c>
       <c r="T26" t="n">
-        <v>40.6</v>
+        <v>40.7</v>
       </c>
       <c r="U26" t="n">
         <v>20.3</v>
       </c>
       <c r="V26" t="n">
-        <v>12.8</v>
+        <v>12.9</v>
       </c>
       <c r="W26" t="n">
-        <v>6.7</v>
+        <v>6.8</v>
       </c>
       <c r="X26" t="n">
-        <v>5.1</v>
+        <v>5</v>
       </c>
       <c r="Y26" t="n">
-        <v>3.7</v>
+        <v>3.8</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.4</v>
+        <v>21.3</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.5</v>
+        <v>97.90000000000001</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.2</v>
+        <v>2.6</v>
       </c>
       <c r="AD26" t="n">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH26" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AI26" t="n">
+        <v>22</v>
+      </c>
+      <c r="AJ26" t="n">
         <v>21</v>
       </c>
-      <c r="AJ26" t="n">
-        <v>22</v>
-      </c>
       <c r="AK26" t="n">
-        <v>9</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
         <v>6</v>
@@ -5137,16 +5204,16 @@
         <v>9</v>
       </c>
       <c r="AN26" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AO26" t="n">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="AP26" t="n">
         <v>18</v>
       </c>
       <c r="AQ26" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AR26" t="n">
         <v>1</v>
@@ -5158,7 +5225,7 @@
         <v>21</v>
       </c>
       <c r="AU26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5167,22 +5234,22 @@
         <v>23</v>
       </c>
       <c r="AX26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AY26" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="BA26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BB26" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>10</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -5289,7 +5356,7 @@
         <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
@@ -5304,13 +5371,13 @@
         <v>4</v>
       </c>
       <c r="AI27" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AJ27" t="n">
         <v>11</v>
       </c>
       <c r="AK27" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AL27" t="n">
         <v>20</v>
@@ -5334,13 +5401,13 @@
         <v>22</v>
       </c>
       <c r="AS27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AT27" t="n">
         <v>25</v>
       </c>
       <c r="AU27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -5510,13 +5577,13 @@
         <v>30</v>
       </c>
       <c r="AQ28" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AR28" t="n">
         <v>30</v>
       </c>
       <c r="AS28" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AT28" t="n">
         <v>24</v>
@@ -5546,7 +5613,7 @@
         <v>20</v>
       </c>
       <c r="BC28" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -5575,28 +5642,28 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E29" t="n">
         <v>16</v>
       </c>
       <c r="F29" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G29" t="n">
-        <v>0.381</v>
+        <v>0.39</v>
       </c>
       <c r="H29" t="n">
         <v>48.4</v>
       </c>
       <c r="I29" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J29" t="n">
         <v>78.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.459</v>
+        <v>0.457</v>
       </c>
       <c r="L29" t="n">
         <v>6.4</v>
@@ -5605,7 +5672,7 @@
         <v>16.7</v>
       </c>
       <c r="N29" t="n">
-        <v>0.382</v>
+        <v>0.38</v>
       </c>
       <c r="O29" t="n">
         <v>19.4</v>
@@ -5614,16 +5681,16 @@
         <v>23.5</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.827</v>
+        <v>0.826</v>
       </c>
       <c r="R29" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="S29" t="n">
-        <v>30.1</v>
+        <v>30.3</v>
       </c>
       <c r="T29" t="n">
-        <v>39.1</v>
+        <v>39.2</v>
       </c>
       <c r="U29" t="n">
         <v>21.7</v>
@@ -5632,49 +5699,49 @@
         <v>13.5</v>
       </c>
       <c r="W29" t="n">
-        <v>6.4</v>
+        <v>6.5</v>
       </c>
       <c r="X29" t="n">
         <v>5</v>
       </c>
       <c r="Y29" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.7</v>
+        <v>19.5</v>
       </c>
       <c r="AA29" t="n">
         <v>20.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC29" t="n">
-        <v>-2.5</v>
+        <v>-2.4</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE29" t="n">
         <v>20</v>
       </c>
       <c r="AF29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AG29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AH29" t="n">
+        <v>17</v>
+      </c>
+      <c r="AI29" t="n">
         <v>23</v>
       </c>
-      <c r="AG29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AH29" t="n">
-        <v>18</v>
-      </c>
-      <c r="AI29" t="n">
-        <v>22</v>
-      </c>
       <c r="AJ29" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AK29" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AL29" t="n">
         <v>18</v>
@@ -5683,7 +5750,7 @@
         <v>19</v>
       </c>
       <c r="AN29" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="AO29" t="n">
         <v>11</v>
@@ -5698,13 +5765,13 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AT29" t="n">
         <v>27</v>
       </c>
       <c r="AU29" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AV29" t="n">
         <v>10</v>
@@ -5713,10 +5780,10 @@
         <v>28</v>
       </c>
       <c r="AX29" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY29" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AZ29" t="n">
         <v>4</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -5835,7 +5902,7 @@
         <v>3.2</v>
       </c>
       <c r="AD30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AE30" t="n">
         <v>8</v>
@@ -5868,19 +5935,19 @@
         <v>24</v>
       </c>
       <c r="AO30" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AP30" t="n">
         <v>4</v>
       </c>
       <c r="AQ30" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
         <v>9</v>
       </c>
       <c r="AS30" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5895,7 +5962,7 @@
         <v>1</v>
       </c>
       <c r="AX30" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AY30" t="n">
         <v>14</v>
@@ -5910,7 +5977,7 @@
         <v>8</v>
       </c>
       <c r="BC30" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="BD30" t="n">
         <v>10</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
@@ -6068,7 +6135,7 @@
         <v>26</v>
       </c>
       <c r="AU31" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AV31" t="n">
         <v>9</v>
@@ -6083,7 +6150,7 @@
         <v>17</v>
       </c>
       <c r="AZ31" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="BA31" t="n">
         <v>28</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-18-2008-09</t>
+          <t>2009-01-18</t>
         </is>
       </c>
     </row>
